--- a/resources/templates/standard/D1100-01.xlsx
+++ b/resources/templates/standard/D1100-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>안전사고 발생 보고서</t>
   </si>
@@ -666,12 +669,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -688,18 +693,18 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="4"/>
     </row>
@@ -789,7 +794,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -804,7 +809,7 @@
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
@@ -821,7 +826,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -836,7 +841,7 @@
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
       <c r="N6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
@@ -853,7 +858,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -868,7 +873,7 @@
       <c r="L7" s="14"/>
       <c r="M7" s="14"/>
       <c r="N7" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
@@ -885,7 +890,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -900,7 +905,7 @@
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
       <c r="N8" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
@@ -917,7 +922,7 @@
     </row>
     <row r="9" ht="30.75" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -1311,7 +1316,7 @@
     </row>
     <row r="23" ht="29.25" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -1593,7 +1598,7 @@
     </row>
     <row r="33" ht="25.5" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -1819,7 +1824,7 @@
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -1849,7 +1854,7 @@
     </row>
     <row r="42" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42" s="24"/>
       <c r="C42" s="24"/>
@@ -1879,7 +1884,7 @@
     </row>
     <row r="43" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -1909,7 +1914,7 @@
     </row>
     <row r="44" ht="20.1" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
